--- a/public/exports-60-250/19438414.xlsx
+++ b/public/exports-60-250/19438414.xlsx
@@ -3964,7 +3964,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">310024942</t>
+          <t xml:space="preserve">310024938</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123773</t>
+          <t xml:space="preserve">311123772</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5779,12 +5779,12 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
